--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/173.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/173.xlsx
@@ -426,13 +426,13 @@
         <v>-5.824646336703793</v>
       </c>
       <c r="E2">
-        <v>-4.243136937154651</v>
+        <v>-4.845754558777368</v>
       </c>
       <c r="F2">
-        <v>-5.139519891550323</v>
+        <v>-4.588592155481614</v>
       </c>
       <c r="G2">
-        <v>-12.06113956552701</v>
+        <v>-11.22257175933854</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.843041758532177</v>
       </c>
       <c r="E3">
-        <v>-6.056233774923685</v>
+        <v>-5.263479115140912</v>
       </c>
       <c r="F3">
-        <v>-4.980158691956271</v>
+        <v>-4.821402468021916</v>
       </c>
       <c r="G3">
-        <v>-11.63886955035635</v>
+        <v>-11.27808960803211</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.909568023567451</v>
       </c>
       <c r="E4">
-        <v>-5.746114817930404</v>
+        <v>-6.594673862909698</v>
       </c>
       <c r="F4">
-        <v>-4.677456269955794</v>
+        <v>-4.663389002161903</v>
       </c>
       <c r="G4">
-        <v>-10.85957375150299</v>
+        <v>-10.38711586595698</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.997701965740529</v>
       </c>
       <c r="E5">
-        <v>-5.814232123953781</v>
+        <v>-5.720207418132522</v>
       </c>
       <c r="F5">
-        <v>-4.856818091555931</v>
+        <v>-4.234283092520627</v>
       </c>
       <c r="G5">
-        <v>-11.10409726612464</v>
+        <v>-9.541864068324724</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.082037578304837</v>
       </c>
       <c r="E6">
-        <v>-7.071898039260024</v>
+        <v>-7.012833152777979</v>
       </c>
       <c r="F6">
-        <v>-4.474412501949134</v>
+        <v>-4.179303157960232</v>
       </c>
       <c r="G6">
-        <v>-10.50347823111682</v>
+        <v>-9.226398873342033</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.13557278973827</v>
       </c>
       <c r="E7">
-        <v>-7.310073129693445</v>
+        <v>-7.632292169235223</v>
       </c>
       <c r="F7">
-        <v>-4.65739309156605</v>
+        <v>-4.514738405673969</v>
       </c>
       <c r="G7">
-        <v>-10.54739261769526</v>
+        <v>-10.58892341148541</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.13729738695916</v>
       </c>
       <c r="E8">
-        <v>-8.667750393459087</v>
+        <v>-9.016637616432035</v>
       </c>
       <c r="F8">
-        <v>-4.714054129955684</v>
+        <v>-4.391085815208287</v>
       </c>
       <c r="G8">
-        <v>-9.62768002979371</v>
+        <v>-10.36824906692868</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.069084455500303</v>
       </c>
       <c r="E9">
-        <v>-9.11391829506481</v>
+        <v>-8.450691577323433</v>
       </c>
       <c r="F9">
-        <v>-4.451818561506517</v>
+        <v>-3.82421095242406</v>
       </c>
       <c r="G9">
-        <v>-9.481592276236752</v>
+        <v>-8.357771313656981</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.922407037591129</v>
       </c>
       <c r="E10">
-        <v>-9.448187603940998</v>
+        <v>-9.898191123031216</v>
       </c>
       <c r="F10">
-        <v>-4.599123799819286</v>
+        <v>-4.555856162356522</v>
       </c>
       <c r="G10">
-        <v>-9.883038959965393</v>
+        <v>-8.19383309855227</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.702404934854429</v>
       </c>
       <c r="E11">
-        <v>-10.58583084414794</v>
+        <v>-11.14872016330137</v>
       </c>
       <c r="F11">
-        <v>-4.602701391482264</v>
+        <v>-4.033806511802895</v>
       </c>
       <c r="G11">
-        <v>-8.678652561141918</v>
+        <v>-8.607247404405378</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.424437917982712</v>
       </c>
       <c r="E12">
-        <v>-10.50345337347441</v>
+        <v>-11.94564554764521</v>
       </c>
       <c r="F12">
-        <v>-4.557549935833086</v>
+        <v>-4.295279525853778</v>
       </c>
       <c r="G12">
-        <v>-8.288829202801658</v>
+        <v>-7.833099503865586</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.117488239444921</v>
       </c>
       <c r="E13">
-        <v>-11.54638810828494</v>
+        <v>-11.90286958216875</v>
       </c>
       <c r="F13">
-        <v>-4.137703162826426</v>
+        <v>-3.93999173263705</v>
       </c>
       <c r="G13">
-        <v>-8.452681343722345</v>
+        <v>-8.502389184994502</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.822601199016153</v>
       </c>
       <c r="E14">
-        <v>-13.99459436868173</v>
+        <v>-13.15258349711753</v>
       </c>
       <c r="F14">
-        <v>-4.049037011591675</v>
+        <v>-3.786717506728989</v>
       </c>
       <c r="G14">
-        <v>-8.579932093160851</v>
+        <v>-7.568322071634676</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.581243756875889</v>
       </c>
       <c r="E15">
-        <v>-13.98208672347254</v>
+        <v>-12.60878622438044</v>
       </c>
       <c r="F15">
-        <v>-4.236053675734089</v>
+        <v>-3.715508545800128</v>
       </c>
       <c r="G15">
-        <v>-8.294983506959163</v>
+        <v>-7.123338403519079</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.434801402810752</v>
       </c>
       <c r="E16">
-        <v>-15.01593733942369</v>
+        <v>-14.46882975218699</v>
       </c>
       <c r="F16">
-        <v>-3.584407786414135</v>
+        <v>-3.527437133518032</v>
       </c>
       <c r="G16">
-        <v>-7.724017028346601</v>
+        <v>-8.021108695586335</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.415283525964799</v>
       </c>
       <c r="E17">
-        <v>-15.34130366840079</v>
+        <v>-15.99603044042977</v>
       </c>
       <c r="F17">
-        <v>-3.560242809703402</v>
+        <v>-3.289140071833689</v>
       </c>
       <c r="G17">
-        <v>-7.659004535046392</v>
+        <v>-6.44188908862442</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.535794789387724</v>
       </c>
       <c r="E18">
-        <v>-16.01862752572805</v>
+        <v>-16.27418289940291</v>
       </c>
       <c r="F18">
-        <v>-3.486461910367867</v>
+        <v>-2.936468560789267</v>
       </c>
       <c r="G18">
-        <v>-6.811680335906551</v>
+        <v>-6.372738413400123</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.79187190100998</v>
       </c>
       <c r="E19">
-        <v>-17.73941142085073</v>
+        <v>-17.28442205187806</v>
       </c>
       <c r="F19">
-        <v>-2.867791153766235</v>
+        <v>-2.802480705519428</v>
       </c>
       <c r="G19">
-        <v>-6.740265247533392</v>
+        <v>-6.71061269113814</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.160061029426712</v>
       </c>
       <c r="E20">
-        <v>-17.29293105453847</v>
+        <v>-18.78133630595754</v>
       </c>
       <c r="F20">
-        <v>-2.760456277200285</v>
+        <v>-2.25751166295756</v>
       </c>
       <c r="G20">
-        <v>-6.475908254585971</v>
+        <v>-6.322772349575903</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.601365878692123</v>
       </c>
       <c r="E21">
-        <v>-17.69508218878964</v>
+        <v>-18.29163165524208</v>
       </c>
       <c r="F21">
-        <v>-2.685608751930701</v>
+        <v>-2.052898442388698</v>
       </c>
       <c r="G21">
-        <v>-6.856740171241571</v>
+        <v>-7.284303748729522</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.071208512591023</v>
       </c>
       <c r="E22">
-        <v>-18.9054708354558</v>
+        <v>-19.48223087049472</v>
       </c>
       <c r="F22">
-        <v>-2.300232921879497</v>
+        <v>-1.885245750474363</v>
       </c>
       <c r="G22">
-        <v>-7.151732952609408</v>
+        <v>-6.337904853235911</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.527429355120606</v>
       </c>
       <c r="E23">
-        <v>-18.9475630013571</v>
+        <v>-19.02123674498789</v>
       </c>
       <c r="F23">
-        <v>-1.993940238568719</v>
+        <v>-1.711520338227275</v>
       </c>
       <c r="G23">
-        <v>-6.697347335162281</v>
+        <v>-6.74768086954136</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.93467314581709</v>
       </c>
       <c r="E24">
-        <v>-18.39424687625589</v>
+        <v>-18.27111313951333</v>
       </c>
       <c r="F24">
-        <v>-2.161714083985585</v>
+        <v>-1.854954207429753</v>
       </c>
       <c r="G24">
-        <v>-7.188086053176145</v>
+        <v>-6.864678859444743</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.2654181134473</v>
       </c>
       <c r="E25">
-        <v>-19.17611961299823</v>
+        <v>-19.69467970009057</v>
       </c>
       <c r="F25">
-        <v>-2.039530380756474</v>
+        <v>-1.95002486538654</v>
       </c>
       <c r="G25">
-        <v>-7.234771366370947</v>
+        <v>-6.266718192504963</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.499695319880536</v>
       </c>
       <c r="E26">
-        <v>-19.22087905009004</v>
+        <v>-19.76522879665606</v>
       </c>
       <c r="F26">
-        <v>-2.027531432888147</v>
+        <v>-2.061284957063908</v>
       </c>
       <c r="G26">
-        <v>-7.472567852456796</v>
+        <v>-6.593813333967113</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.623977537218506</v>
       </c>
       <c r="E27">
-        <v>-19.92937239401209</v>
+        <v>-18.89556706280103</v>
       </c>
       <c r="F27">
-        <v>-2.117883439069883</v>
+        <v>-2.009461348392983</v>
       </c>
       <c r="G27">
-        <v>-7.61750022562055</v>
+        <v>-8.096556028426326</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.62973226098663</v>
       </c>
       <c r="E28">
-        <v>-19.13545844488336</v>
+        <v>-20.08475339416328</v>
       </c>
       <c r="F28">
-        <v>-2.07862653683797</v>
+        <v>-1.845991223801323</v>
       </c>
       <c r="G28">
-        <v>-8.705653370560213</v>
+        <v>-7.653866568369444</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.513616255093071</v>
       </c>
       <c r="E29">
-        <v>-19.11203717731568</v>
+        <v>-19.53338904135937</v>
       </c>
       <c r="F29">
-        <v>-2.274923717644858</v>
+        <v>-1.609798115425642</v>
       </c>
       <c r="G29">
-        <v>-7.861904560602785</v>
+        <v>-7.61250130185625</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.279395570040249</v>
       </c>
       <c r="E30">
-        <v>-18.80720294948935</v>
+        <v>-18.816441036465</v>
       </c>
       <c r="F30">
-        <v>-1.620322633086694</v>
+        <v>-1.626408023066771</v>
       </c>
       <c r="G30">
-        <v>-7.711824289125465</v>
+        <v>-7.542830870982288</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.936259474548918</v>
       </c>
       <c r="E31">
-        <v>-19.08999709432035</v>
+        <v>-18.70163969189655</v>
       </c>
       <c r="F31">
-        <v>-2.150798390963419</v>
+        <v>-1.750433576275538</v>
       </c>
       <c r="G31">
-        <v>-8.022214417796453</v>
+        <v>-7.818605935494657</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.499008755654146</v>
       </c>
       <c r="E32">
-        <v>-18.8219884171244</v>
+        <v>-17.54609992241129</v>
       </c>
       <c r="F32">
-        <v>-1.886414525439957</v>
+        <v>-1.542984730265082</v>
       </c>
       <c r="G32">
-        <v>-8.184351696127798</v>
+        <v>-7.694486962136302</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.989968113153758</v>
       </c>
       <c r="E33">
-        <v>-18.03775181695006</v>
+        <v>-17.6043179842539</v>
       </c>
       <c r="F33">
-        <v>-1.711279614928128</v>
+        <v>-1.788548626542419</v>
       </c>
       <c r="G33">
-        <v>-7.725099576737942</v>
+        <v>-7.292417895846277</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.432326297417541</v>
       </c>
       <c r="E34">
-        <v>-18.50354159643101</v>
+        <v>-17.16267402818184</v>
       </c>
       <c r="F34">
-        <v>-2.099227383386006</v>
+        <v>-1.660428401689283</v>
       </c>
       <c r="G34">
-        <v>-7.71002666289764</v>
+        <v>-7.111056279568383</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.849787255890838</v>
       </c>
       <c r="E35">
-        <v>-16.69012323700743</v>
+        <v>-17.23775612722902</v>
       </c>
       <c r="F35">
-        <v>-1.723841570249394</v>
+        <v>-1.696632710769187</v>
       </c>
       <c r="G35">
-        <v>-7.108672686780108</v>
+        <v>-7.66351680861642</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.2710805544806</v>
       </c>
       <c r="E36">
-        <v>-16.73540797708414</v>
+        <v>-17.33856901558778</v>
       </c>
       <c r="F36">
-        <v>-1.816071059793883</v>
+        <v>-1.399196110937546</v>
       </c>
       <c r="G36">
-        <v>-6.679612742708405</v>
+        <v>-6.544330609791627</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.722473603158065</v>
       </c>
       <c r="E37">
-        <v>-16.5931006813931</v>
+        <v>-16.46800611540521</v>
       </c>
       <c r="F37">
-        <v>-2.004616791997654</v>
+        <v>-1.655159412108616</v>
       </c>
       <c r="G37">
-        <v>-6.647613009525809</v>
+        <v>-6.245931277063879</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.224681756046903</v>
       </c>
       <c r="E38">
-        <v>-15.98279823937936</v>
+        <v>-15.36620121849497</v>
       </c>
       <c r="F38">
-        <v>-2.031625312679558</v>
+        <v>-1.87211682843537</v>
       </c>
       <c r="G38">
-        <v>-6.394379449590339</v>
+        <v>-7.12801620436607</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.796291802036069</v>
       </c>
       <c r="E39">
-        <v>-15.3958581947712</v>
+        <v>-15.23613891652067</v>
       </c>
       <c r="F39">
-        <v>-2.048394382765188</v>
+        <v>-1.332412024336423</v>
       </c>
       <c r="G39">
-        <v>-6.394525113594066</v>
+        <v>-6.910993391539146</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.450312913822826</v>
       </c>
       <c r="E40">
-        <v>-15.21529435066336</v>
+        <v>-14.6438235732654</v>
       </c>
       <c r="F40">
-        <v>-1.857073205944611</v>
+        <v>-1.652174126458013</v>
       </c>
       <c r="G40">
-        <v>-6.847089930994595</v>
+        <v>-5.687094637307206</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.191767679516949</v>
       </c>
       <c r="E41">
-        <v>-14.62546966811231</v>
+        <v>-14.58896563913648</v>
       </c>
       <c r="F41">
-        <v>-1.915268063513349</v>
+        <v>-1.323919401364879</v>
       </c>
       <c r="G41">
-        <v>-7.264394127856346</v>
+        <v>-5.744122094766692</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.021035755663413</v>
       </c>
       <c r="E42">
-        <v>-15.58693262705084</v>
+        <v>-15.22347277472121</v>
       </c>
       <c r="F42">
-        <v>-1.741260751613313</v>
+        <v>-1.766446426786546</v>
       </c>
       <c r="G42">
-        <v>-7.225511770497605</v>
+        <v>-5.038899752354526</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.932504986401082</v>
       </c>
       <c r="E43">
-        <v>-14.29436123409348</v>
+        <v>-14.56106118230121</v>
       </c>
       <c r="F43">
-        <v>-2.011021298719691</v>
+        <v>-1.438163986839892</v>
       </c>
       <c r="G43">
-        <v>-6.178535190975396</v>
+        <v>-6.44915242553758</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.912558366152203</v>
       </c>
       <c r="E44">
-        <v>-13.06851690563913</v>
+        <v>-12.73683788389533</v>
       </c>
       <c r="F44">
-        <v>-1.60369372097458</v>
+        <v>-1.996274621088076</v>
       </c>
       <c r="G44">
-        <v>-6.632397742227319</v>
+        <v>-6.408565137226115</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.943883264863788</v>
       </c>
       <c r="E45">
-        <v>-13.1716981859039</v>
+        <v>-11.90574516316362</v>
       </c>
       <c r="F45">
-        <v>-1.932387132606291</v>
+        <v>-1.728377303991213</v>
       </c>
       <c r="G45">
-        <v>-6.577191084814433</v>
+        <v>-5.387109553266148</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.008698778169931</v>
       </c>
       <c r="E46">
-        <v>-13.06699080989855</v>
+        <v>-11.32239166996954</v>
       </c>
       <c r="F46">
-        <v>-2.191600198315843</v>
+        <v>-1.958923708925395</v>
       </c>
       <c r="G46">
-        <v>-7.034787931434654</v>
+        <v>-5.861689498502829</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.089855568990266</v>
       </c>
       <c r="E47">
-        <v>-13.27490210853871</v>
+        <v>-11.93363603457687</v>
       </c>
       <c r="F47">
-        <v>-2.017603972357215</v>
+        <v>-2.332306134078976</v>
       </c>
       <c r="G47">
-        <v>-7.000186109458191</v>
+        <v>-5.494089832367696</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.176253844802318</v>
       </c>
       <c r="E48">
-        <v>-11.02018395706765</v>
+        <v>-11.79380581416802</v>
       </c>
       <c r="F48">
-        <v>-1.943395472424511</v>
+        <v>-2.120257414237127</v>
       </c>
       <c r="G48">
-        <v>-6.522659778691557</v>
+        <v>-6.126195465999519</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.26361686269198</v>
       </c>
       <c r="E49">
-        <v>-11.58093130801545</v>
+        <v>-10.71253754688256</v>
       </c>
       <c r="F49">
-        <v>-1.949179166427696</v>
+        <v>-2.267120798599489</v>
       </c>
       <c r="G49">
-        <v>-6.738331888938458</v>
+        <v>-6.650195235046441</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.353572233711731</v>
       </c>
       <c r="E50">
-        <v>-11.05716347581429</v>
+        <v>-10.02093993948313</v>
       </c>
       <c r="F50">
-        <v>-2.46304184925146</v>
+        <v>-2.441269852178956</v>
       </c>
       <c r="G50">
-        <v>-6.858726498565133</v>
+        <v>-5.978684177860673</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.456738526981227</v>
       </c>
       <c r="E51">
-        <v>-9.706763469778975</v>
+        <v>-11.03387806246685</v>
       </c>
       <c r="F51">
-        <v>-2.29660623533314</v>
+        <v>-2.394239329461109</v>
       </c>
       <c r="G51">
-        <v>-6.42407835362314</v>
+        <v>-5.365809503266477</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.587236868033851</v>
       </c>
       <c r="E52">
-        <v>-9.908869264741304</v>
+        <v>-10.24937428232605</v>
       </c>
       <c r="F52">
-        <v>-2.560975847503363</v>
+        <v>-2.082395756916716</v>
       </c>
       <c r="G52">
-        <v>-6.414024226820374</v>
+        <v>-5.457706936891106</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.757749863426712</v>
       </c>
       <c r="E53">
-        <v>-9.136782560329538</v>
+        <v>-10.83822081449144</v>
       </c>
       <c r="F53">
-        <v>-2.450523445842869</v>
+        <v>-1.805004122856793</v>
       </c>
       <c r="G53">
-        <v>-6.495082934349429</v>
+        <v>-5.555963928496674</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.984176681994855</v>
       </c>
       <c r="E54">
-        <v>-8.933449548911131</v>
+        <v>-8.923853712488878</v>
       </c>
       <c r="F54">
-        <v>-2.555914323397618</v>
+        <v>-2.413683278837917</v>
       </c>
       <c r="G54">
-        <v>-6.458140556676701</v>
+        <v>-6.528800840666906</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.276941797999414</v>
       </c>
       <c r="E55">
-        <v>-8.406004595815741</v>
+        <v>-8.384915492362021</v>
       </c>
       <c r="F55">
-        <v>-2.465598742451937</v>
+        <v>-2.445030361875167</v>
       </c>
       <c r="G55">
-        <v>-6.58951624585714</v>
+        <v>-5.61040584988999</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.638108109224542</v>
       </c>
       <c r="E56">
-        <v>-9.084496799436975</v>
+        <v>-8.6460318321183</v>
       </c>
       <c r="F56">
-        <v>-2.379418217651469</v>
+        <v>-2.088775716197063</v>
       </c>
       <c r="G56">
-        <v>-7.06087834082965</v>
+        <v>-5.679765089483261</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.067830624018738</v>
       </c>
       <c r="E57">
-        <v>-7.774649278140347</v>
+        <v>-8.893091788554772</v>
       </c>
       <c r="F57">
-        <v>-2.417487340446802</v>
+        <v>-2.868208460274953</v>
       </c>
       <c r="G57">
-        <v>-7.247665941246408</v>
+        <v>-6.150087673156439</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.556020080106038</v>
       </c>
       <c r="E58">
-        <v>-8.440027021035368</v>
+        <v>-8.645338975595127</v>
       </c>
       <c r="F58">
-        <v>-2.347129621447489</v>
+        <v>-2.370094149074319</v>
       </c>
       <c r="G58">
-        <v>-7.794121140686207</v>
+        <v>-6.169537128199657</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.082321700786424</v>
       </c>
       <c r="E59">
-        <v>-7.768024120667126</v>
+        <v>-6.366465943767158</v>
       </c>
       <c r="F59">
-        <v>-2.366182395463184</v>
+        <v>-2.606098796446063</v>
       </c>
       <c r="G59">
-        <v>-6.372625854851788</v>
+        <v>-6.35317308926303</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.625768705467315</v>
       </c>
       <c r="E60">
-        <v>-8.1368230438518</v>
+        <v>-7.694373019406376</v>
       </c>
       <c r="F60">
-        <v>-2.99572766873318</v>
+        <v>-2.204054461634859</v>
       </c>
       <c r="G60">
-        <v>-6.907682845999876</v>
+        <v>-6.174155339226941</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.162830651658829</v>
       </c>
       <c r="E61">
-        <v>-7.200044796729079</v>
+        <v>-7.470738859011583</v>
       </c>
       <c r="F61">
-        <v>-2.463879629680727</v>
+        <v>-2.528157501670668</v>
       </c>
       <c r="G61">
-        <v>-7.108765382055207</v>
+        <v>-6.479728624138289</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.667607814695129</v>
       </c>
       <c r="E62">
-        <v>-6.927792939387937</v>
+        <v>-6.639795577922126</v>
       </c>
       <c r="F62">
-        <v>-2.546652811204128</v>
+        <v>-2.356177333342395</v>
       </c>
       <c r="G62">
-        <v>-7.495228536673108</v>
+        <v>-6.995822810437431</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.118276290608177</v>
       </c>
       <c r="E63">
-        <v>-7.286126559140885</v>
+        <v>-7.271399961667941</v>
       </c>
       <c r="F63">
-        <v>-2.59088967668714</v>
+        <v>-3.072192949595385</v>
       </c>
       <c r="G63">
-        <v>-7.113370350900333</v>
+        <v>-6.011173871783081</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.496445905506819</v>
       </c>
       <c r="E64">
-        <v>-6.488929466356588</v>
+        <v>-5.982193224898275</v>
       </c>
       <c r="F64">
-        <v>-2.566597211650215</v>
+        <v>-2.425829511356379</v>
       </c>
       <c r="G64">
-        <v>-7.267933101037826</v>
+        <v>-6.5439068599626</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.787813446856525</v>
       </c>
       <c r="E65">
-        <v>-5.82284528151637</v>
+        <v>-7.089314550293524</v>
       </c>
       <c r="F65">
-        <v>-2.590261737291669</v>
+        <v>-2.687748338622459</v>
       </c>
       <c r="G65">
-        <v>-7.552259304678133</v>
+        <v>-7.130204474967528</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.986359546174798</v>
       </c>
       <c r="E66">
-        <v>-7.779005670135727</v>
+        <v>-7.327833804751529</v>
       </c>
       <c r="F66">
-        <v>-2.755920543458466</v>
+        <v>-2.870934018155425</v>
       </c>
       <c r="G66">
-        <v>-7.612971399322827</v>
+        <v>-6.316727293421193</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.094107564848345</v>
       </c>
       <c r="E67">
-        <v>-6.6387178011083</v>
+        <v>-5.718767363398082</v>
       </c>
       <c r="F67">
-        <v>-2.757588185787423</v>
+        <v>-2.528359424174887</v>
       </c>
       <c r="G67">
-        <v>-7.09017335830666</v>
+        <v>-7.146055367009558</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.118575159674018</v>
       </c>
       <c r="E68">
-        <v>-6.719510305879147</v>
+        <v>-5.946862070690431</v>
       </c>
       <c r="F68">
-        <v>-3.015420259938712</v>
+        <v>-3.076488751891015</v>
       </c>
       <c r="G68">
-        <v>-7.149544682007949</v>
+        <v>-6.592955902672442</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.071048547820537</v>
       </c>
       <c r="E69">
-        <v>-5.79673862886215</v>
+        <v>-6.110099973244924</v>
       </c>
       <c r="F69">
-        <v>-2.625132565990772</v>
+        <v>-2.709869542849317</v>
       </c>
       <c r="G69">
-        <v>-7.10984130935547</v>
+        <v>-6.739176078050972</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.966136378114697</v>
       </c>
       <c r="E70">
-        <v>-5.683476965456307</v>
+        <v>-6.772787802579389</v>
       </c>
       <c r="F70">
-        <v>-2.735075806199452</v>
+        <v>-2.820919793492889</v>
       </c>
       <c r="G70">
-        <v>-7.430924500118304</v>
+        <v>-6.729423210892279</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.820184421100522</v>
       </c>
       <c r="E71">
-        <v>-7.211773544408945</v>
+        <v>-6.773485187576569</v>
       </c>
       <c r="F71">
-        <v>-2.88140231425648</v>
+        <v>-2.773534520649983</v>
       </c>
       <c r="G71">
-        <v>-7.637777317048586</v>
+        <v>-7.580782965044493</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.647287054480071</v>
       </c>
       <c r="E72">
-        <v>-6.218407486086376</v>
+        <v>-7.033953955549753</v>
       </c>
       <c r="F72">
-        <v>-2.993588873894379</v>
+        <v>-3.06497520988577</v>
       </c>
       <c r="G72">
-        <v>-7.678348052632354</v>
+        <v>-6.719511437547701</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.460097602684216</v>
       </c>
       <c r="E73">
-        <v>-5.56248519691937</v>
+        <v>-5.808082456251364</v>
       </c>
       <c r="F73">
-        <v>-2.792493064163709</v>
+        <v>-3.152515346214643</v>
       </c>
       <c r="G73">
-        <v>-7.40895903046524</v>
+        <v>-6.985742199270351</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.270166879000437</v>
       </c>
       <c r="E74">
-        <v>-5.339000476166831</v>
+        <v>-7.185512923638464</v>
       </c>
       <c r="F74">
-        <v>-2.837430719514303</v>
+        <v>-2.970186451581931</v>
       </c>
       <c r="G74">
-        <v>-6.921117039798238</v>
+        <v>-6.554964082063766</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.081862576717239</v>
       </c>
       <c r="E75">
-        <v>-7.046955204425775</v>
+        <v>-8.511241803279992</v>
       </c>
       <c r="F75">
-        <v>-2.932799114183194</v>
+        <v>-3.202800384588719</v>
       </c>
       <c r="G75">
-        <v>-6.79664714861272</v>
+        <v>-6.77179819379495</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.896683291402872</v>
       </c>
       <c r="E76">
-        <v>-7.472187970694037</v>
+        <v>-8.63003726192321</v>
       </c>
       <c r="F76">
-        <v>-3.129299801200216</v>
+        <v>-3.195704590234592</v>
       </c>
       <c r="G76">
-        <v>-7.156437237820713</v>
+        <v>-6.836095609258675</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.716040528228609</v>
       </c>
       <c r="E77">
-        <v>-7.545186971697683</v>
+        <v>-9.321566942212527</v>
       </c>
       <c r="F77">
-        <v>-3.233328691667687</v>
+        <v>-3.129880229418225</v>
       </c>
       <c r="G77">
-        <v>-7.336693131888489</v>
+        <v>-6.537606891801367</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.53780926989281</v>
       </c>
       <c r="E78">
-        <v>-8.134889385450524</v>
+        <v>-8.140060902767285</v>
       </c>
       <c r="F78">
-        <v>-3.2206978451391</v>
+        <v>-2.93413734568174</v>
       </c>
       <c r="G78">
-        <v>-6.954166215916782</v>
+        <v>-6.971079793076918</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.358399917732444</v>
       </c>
       <c r="E79">
-        <v>-8.770293158888775</v>
+        <v>-8.8827170546032</v>
       </c>
       <c r="F79">
-        <v>-3.346193077437395</v>
+        <v>-2.935629196654084</v>
       </c>
       <c r="G79">
-        <v>-7.742662020823776</v>
+        <v>-6.205986234587034</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.175543352275292</v>
       </c>
       <c r="E80">
-        <v>-9.547035134580426</v>
+        <v>-9.331937147690091</v>
       </c>
       <c r="F80">
-        <v>-3.166805124689653</v>
+        <v>-3.430040803424421</v>
       </c>
       <c r="G80">
-        <v>-7.079188968207358</v>
+        <v>-6.553960986765367</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.986278011495958</v>
       </c>
       <c r="E81">
-        <v>-10.46614780459922</v>
+        <v>-10.21269817133793</v>
       </c>
       <c r="F81">
-        <v>-3.361124256808158</v>
+        <v>-3.313074619333725</v>
       </c>
       <c r="G81">
-        <v>-7.03307968993639</v>
+        <v>-7.088137372800008</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.786920590990217</v>
       </c>
       <c r="E82">
-        <v>-10.37226800994621</v>
+        <v>-11.27023270634919</v>
       </c>
       <c r="F82">
-        <v>-3.485750826411834</v>
+        <v>-3.301073295906525</v>
       </c>
       <c r="G82">
-        <v>-7.226984963262582</v>
+        <v>-6.220105711312025</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.576013747649881</v>
       </c>
       <c r="E83">
-        <v>-11.68441146756473</v>
+        <v>-11.99933513548015</v>
       </c>
       <c r="F83">
-        <v>-3.268125878041723</v>
+        <v>-3.394410587738864</v>
       </c>
       <c r="G83">
-        <v>-6.899876579618274</v>
+        <v>-5.9450424140906</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.354648618910147</v>
       </c>
       <c r="E84">
-        <v>-12.38605775878718</v>
+        <v>-13.59084468310586</v>
       </c>
       <c r="F84">
-        <v>-3.38934906363312</v>
+        <v>-3.647505005644116</v>
       </c>
       <c r="G84">
-        <v>-7.203440363387284</v>
+        <v>-6.021688164415806</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.124396922550601</v>
       </c>
       <c r="E85">
-        <v>-14.11629257916386</v>
+        <v>-14.3793289918994</v>
       </c>
       <c r="F85">
-        <v>-3.79106161205504</v>
+        <v>-3.489515295372834</v>
       </c>
       <c r="G85">
-        <v>-7.874805756569325</v>
+        <v>-6.475799006583174</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.888673384450423</v>
       </c>
       <c r="E86">
-        <v>-13.61304326269146</v>
+        <v>-15.73903501202047</v>
       </c>
       <c r="F86">
-        <v>-3.969938027792094</v>
+        <v>-3.31317360095344</v>
       </c>
       <c r="G86">
-        <v>-6.962273741942457</v>
+        <v>-6.34899518079247</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.653877360344042</v>
       </c>
       <c r="E87">
-        <v>-16.08606556065028</v>
+        <v>-16.61999528852465</v>
       </c>
       <c r="F87">
-        <v>-4.45161584714934</v>
+        <v>-3.660409041443116</v>
       </c>
       <c r="G87">
-        <v>-7.289044449941759</v>
+        <v>-5.55607648704501</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.424846082660303</v>
       </c>
       <c r="E88">
-        <v>-17.55353114825788</v>
+        <v>-18.23230411726759</v>
       </c>
       <c r="F88">
-        <v>-3.753962509132913</v>
+        <v>-3.726865300919744</v>
       </c>
       <c r="G88">
-        <v>-6.399586937723612</v>
+        <v>-5.936924956428307</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.206681546504316</v>
       </c>
       <c r="E89">
-        <v>-18.70425714987299</v>
+        <v>-18.07179235606571</v>
       </c>
       <c r="F89">
-        <v>-3.96009133626285</v>
+        <v>-3.938412777839357</v>
       </c>
       <c r="G89">
-        <v>-6.836158509623921</v>
+        <v>-5.849245157820709</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.007604963717544</v>
       </c>
       <c r="E90">
-        <v>-20.49208057420521</v>
+        <v>-19.48836242430111</v>
       </c>
       <c r="F90">
-        <v>-4.13467353341019</v>
+        <v>-3.63216127088238</v>
       </c>
       <c r="G90">
-        <v>-7.113376971991412</v>
+        <v>-6.188592628323702</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.833732053006974</v>
       </c>
       <c r="E91">
-        <v>-21.75132692694013</v>
+        <v>-22.07729554296026</v>
       </c>
       <c r="F91">
-        <v>-4.016472058705451</v>
+        <v>-3.919956269100826</v>
       </c>
       <c r="G91">
-        <v>-7.155649327982366</v>
+        <v>-5.708540351310606</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.69118985505842</v>
       </c>
       <c r="E92">
-        <v>-23.93401517084518</v>
+        <v>-23.83957384541522</v>
       </c>
       <c r="F92">
-        <v>-3.910301205987349</v>
+        <v>-3.824758914670802</v>
       </c>
       <c r="G92">
-        <v>-7.135061045273638</v>
+        <v>-6.332439142550575</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.588297643103553</v>
       </c>
       <c r="E93">
-        <v>-26.20206967826883</v>
+        <v>-27.25343643168164</v>
       </c>
       <c r="F93">
-        <v>-4.16785454789752</v>
+        <v>-4.045753197376012</v>
       </c>
       <c r="G93">
-        <v>-8.121275871968065</v>
+        <v>-6.444924858883931</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.529103001171104</v>
       </c>
       <c r="E94">
-        <v>-28.23152794717634</v>
+        <v>-27.80244144952755</v>
       </c>
       <c r="F94">
-        <v>-4.15546759207991</v>
+        <v>-3.85648925453959</v>
       </c>
       <c r="G94">
-        <v>-7.197064252678649</v>
+        <v>-6.202943843236443</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.516027963224793</v>
       </c>
       <c r="E95">
-        <v>-30.327792528882</v>
+        <v>-31.15863165506928</v>
       </c>
       <c r="F95">
-        <v>-3.951576541408489</v>
+        <v>-4.058401464669669</v>
       </c>
       <c r="G95">
-        <v>-7.946601557679498</v>
+        <v>-7.453254129780689</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.558064118214852</v>
       </c>
       <c r="E96">
-        <v>-33.2457781543605</v>
+        <v>-33.73505260004524</v>
       </c>
       <c r="F96">
-        <v>-3.817517419372455</v>
+        <v>-4.000944614057525</v>
       </c>
       <c r="G96">
-        <v>-7.887236855069288</v>
+        <v>-6.915237510920492</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.650349712682433</v>
       </c>
       <c r="E97">
-        <v>-35.03789683628901</v>
+        <v>-35.63421308633005</v>
       </c>
       <c r="F97">
-        <v>-3.796108882807545</v>
+        <v>-3.877400507447052</v>
       </c>
       <c r="G97">
-        <v>-7.829828684872786</v>
+        <v>-7.752977680724145</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.811730081176085</v>
       </c>
       <c r="E98">
-        <v>-38.99377021229649</v>
+        <v>-38.62099528893308</v>
       </c>
       <c r="F98">
-        <v>-3.731906236848588</v>
+        <v>-4.050551034446835</v>
       </c>
       <c r="G98">
-        <v>-8.238542016060128</v>
+        <v>-7.417126146310622</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.029192564812069</v>
       </c>
       <c r="E99">
-        <v>-40.41553896869269</v>
+        <v>-40.39845077202474</v>
       </c>
       <c r="F99">
-        <v>-4.189068288634831</v>
+        <v>-3.977459047184516</v>
       </c>
       <c r="G99">
-        <v>-8.921775715000456</v>
+        <v>-8.782090556516447</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.340602542369495</v>
       </c>
       <c r="E100">
-        <v>-43.67631422689281</v>
+        <v>-44.22963488046803</v>
       </c>
       <c r="F100">
-        <v>-3.250564954998373</v>
+        <v>-3.511226319767593</v>
       </c>
       <c r="G100">
-        <v>-9.314661327964542</v>
+        <v>-8.565044569870748</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.701147025839112</v>
       </c>
       <c r="E101">
-        <v>-45.82992740343161</v>
+        <v>-46.77442217026341</v>
       </c>
       <c r="F101">
-        <v>-3.908605848804871</v>
+        <v>-3.71387574500131</v>
       </c>
       <c r="G101">
-        <v>-10.57956118870035</v>
+        <v>-8.877904365514034</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.201348982797501</v>
       </c>
       <c r="E102">
-        <v>-48.54289089668685</v>
+        <v>-49.72737553991064</v>
       </c>
       <c r="F102">
-        <v>-3.562252532510095</v>
+        <v>-3.821368992158805</v>
       </c>
       <c r="G102">
-        <v>-10.26981661640952</v>
+        <v>-9.201046715602294</v>
       </c>
     </row>
   </sheetData>
